--- a/数字（すうじ）.xlsx
+++ b/数字（すうじ）.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3EE64B-83A2-4AA1-8165-F28A8BA19292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC133E9-23C1-4F00-951F-67F50A1B78CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="特殊「とくしゅ」" sheetId="2" r:id="rId1"/>
     <sheet name="指標（しひょう）" sheetId="3" r:id="rId2"/>
     <sheet name="符号（ふごう）" sheetId="4" r:id="rId3"/>
     <sheet name="数字（すうじ）" sheetId="1" r:id="rId4"/>
@@ -39,92 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="271">
   <si>
     <t>っつ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>八王子市｜はちおうじし</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>今日｜きょう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何十年、何百年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>だいめ（代目）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>こ（個）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>いちこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>にこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さんこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>よこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ろくこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ななこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>はちこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>きゅうこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>じゅうこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>いこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さい（歳）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さつ（冊）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>かい（階)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>つぎ（次）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>かい（回）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>三つ（みっつ）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,10 +74,6 @@
   </si>
   <si>
     <t>四人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>よにんｎ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1274,6 +1190,38 @@
   </si>
   <si>
     <t>けたちがい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よにん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代目「だいめ」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次（つぎ）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回（かい）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>階（かい）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冊（さつ）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>歳（さい）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>個（こ）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1662,42 +1610,42 @@
   <sheetData>
     <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1722,620 +1670,620 @@
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="J1" s="1" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A26" s="5" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A27" s="5" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H27" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="F31" s="1" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="F32" s="1" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="6:7" ht="18" x14ac:dyDescent="0.45">
       <c r="F33" s="1" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="6:7" ht="18" x14ac:dyDescent="0.45">
       <c r="F34" s="1" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -2354,54 +2302,54 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2412,14 +2360,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.5546875" customWidth="1"/>
     <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -2427,390 +2376,364 @@
     <col min="12" max="16" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="R1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>227</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>260</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>228</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>229</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>230</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>231</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>232</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>233</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>234</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>235</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>236</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.45">
+      <c r="F12" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="18" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
+      </c>
+      <c r="F15" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="D30" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="C31" s="3"/>
     </row>
     <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
